--- a/analysis/aggregate/multiset-PRF.xlsx
+++ b/analysis/aggregate/multiset-PRF.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y9"/>
+  <dimension ref="A1:Y17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -551,7 +551,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -578,58 +578,58 @@
         <v>5</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6085131776978114</v>
+        <v>0.5896153400840919</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01900074019798977</v>
+        <v>0.008927634446055845</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6047058823529412</v>
+        <v>0.5847058823529412</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01341382853057812</v>
+        <v>0.007892004626469874</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6065466457884552</v>
+        <v>0.5871284510430088</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01505052797827696</v>
+        <v>0.007398071636777081</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6192837465564739</v>
+        <v>0.6027548209366392</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01369121062235724</v>
+        <v>0.010149935772419</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6214876033057851</v>
+        <v>0.6022038567493113</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.01206315925389064</v>
+        <v>0.009661530532644701</v>
       </c>
       <c r="R2" t="n">
-        <v>0.6167493112947657</v>
+        <v>0.5978512396694213</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01255545719988956</v>
+        <v>0.009775539445164426</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6109803921568627</v>
+        <v>0.5958823529411765</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01509931239857134</v>
+        <v>0.008752436910064981</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6047058823529412</v>
+        <v>0.5847058823529412</v>
       </c>
       <c r="W2" t="n">
-        <v>0.01341382853057812</v>
+        <v>0.007892004626469874</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6034509803921567</v>
+        <v>0.5848627450980393</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.01361128961271437</v>
+        <v>0.008087373691482448</v>
       </c>
     </row>
     <row r="3">
@@ -640,7 +640,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -667,58 +667,58 @@
         <v>5</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6085131776978114</v>
+        <v>0.557504926942833</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01900074019798977</v>
+        <v>0.01676012661093303</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6047058823529412</v>
+        <v>0.5588235294117647</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01341382853057812</v>
+        <v>0.01764705882352943</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6065466457884552</v>
+        <v>0.5581565311300726</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01505052797827696</v>
+        <v>0.01706725013505337</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6192837465564739</v>
+        <v>0.5753443526170801</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01369121062235724</v>
+        <v>0.01838726897627025</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6214876033057851</v>
+        <v>0.5771349862258953</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01206315925389064</v>
+        <v>0.01573506840054526</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6167493112947657</v>
+        <v>0.5658559622195984</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01255545719988956</v>
+        <v>0.01689606040553306</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6109803921568627</v>
+        <v>0.5742156862745097</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01509931239857134</v>
+        <v>0.02243577702541931</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6047058823529412</v>
+        <v>0.5588235294117647</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01341382853057812</v>
+        <v>0.01764705882352943</v>
       </c>
       <c r="X3" t="n">
-        <v>0.6034509803921567</v>
+        <v>0.5527002801120446</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.01361128961271437</v>
+        <v>0.01958351431853355</v>
       </c>
     </row>
     <row r="4">
@@ -729,7 +729,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -756,58 +756,58 @@
         <v>5</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6089705445422638</v>
+        <v>0.5740157127939933</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01801028558349509</v>
+        <v>0.0165149354316568</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6058823529411764</v>
+        <v>0.5705882352941176</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0110048746669822</v>
+        <v>0.01440876319284219</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6073734320064142</v>
+        <v>0.5722928044339168</v>
       </c>
       <c r="M4" t="n">
-        <v>0.01350946643807132</v>
+        <v>0.01539271601654646</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6060606060606062</v>
+        <v>0.5757575757575759</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0151515151515151</v>
+        <v>0.02116018112360495</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6090909090909091</v>
+        <v>0.5694214876033058</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.01300905669765022</v>
+        <v>0.02101623264216045</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6031404958677685</v>
+        <v>0.5682093663911845</v>
       </c>
       <c r="S4" t="n">
-        <v>0.01341346048639007</v>
+        <v>0.02090544290305585</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6115686274509804</v>
+        <v>0.5880392156862745</v>
       </c>
       <c r="U4" t="n">
-        <v>0.01517867441059154</v>
+        <v>0.01641095647739284</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6058823529411764</v>
+        <v>0.5705882352941176</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0110048746669822</v>
+        <v>0.01440876319284219</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6032941176470588</v>
+        <v>0.5738039215686274</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.01222812761462815</v>
+        <v>0.01540782267601536</v>
       </c>
     </row>
     <row r="5">
@@ -818,7 +818,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -845,58 +845,58 @@
         <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6089705445422638</v>
+        <v>0.5344662936228443</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01801028558349509</v>
+        <v>0.02067948964304349</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6058823529411764</v>
+        <v>0.5388235294117647</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0110048746669822</v>
+        <v>0.02020654592625613</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6073734320064142</v>
+        <v>0.5366236925916494</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01350946643807132</v>
+        <v>0.0202264023160756</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6060606060606062</v>
+        <v>0.5546005509641875</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0151515151515151</v>
+        <v>0.02262155057937219</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6090909090909091</v>
+        <v>0.5476584022038569</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.01300905669765022</v>
+        <v>0.02453569788125821</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6031404958677685</v>
+        <v>0.541806375442739</v>
       </c>
       <c r="S5" t="n">
-        <v>0.01341346048639007</v>
+        <v>0.0231798487821793</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6115686274509804</v>
+        <v>0.562078431372549</v>
       </c>
       <c r="U5" t="n">
-        <v>0.01517867441059154</v>
+        <v>0.02061825542443885</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6058823529411764</v>
+        <v>0.5388235294117647</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0110048746669822</v>
+        <v>0.02020654592625613</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6032941176470588</v>
+        <v>0.537268907563025</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.01222812761462815</v>
+        <v>0.01989914172312257</v>
       </c>
     </row>
     <row r="6">
@@ -907,7 +907,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -917,7 +917,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -931,61 +931,61 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6183372367284565</v>
+        <v>0.6041234314495487</v>
       </c>
       <c r="I6" t="n">
-        <v>0.008663292355168311</v>
+        <v>0.02059079513146542</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6085714285714285</v>
+        <v>0.5874285714285714</v>
       </c>
       <c r="K6" t="n">
-        <v>0.009897433186107876</v>
+        <v>0.01779704171702561</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6133829977006118</v>
+        <v>0.5956269772817006</v>
       </c>
       <c r="M6" t="n">
-        <v>0.007763048768872636</v>
+        <v>0.01855125039611551</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6291322314049587</v>
+        <v>0.6159779614325068</v>
       </c>
       <c r="O6" t="n">
-        <v>0.003956310362629474</v>
+        <v>0.01375342800701559</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6287878787878788</v>
+        <v>0.6027548209366391</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.006794604493548555</v>
+        <v>0.0166888498411691</v>
       </c>
       <c r="R6" t="n">
-        <v>0.625491932310114</v>
+        <v>0.6049901613537976</v>
       </c>
       <c r="S6" t="n">
-        <v>0.004619919287070238</v>
+        <v>0.01475456867549878</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6190476190476191</v>
+        <v>0.616</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0111879429756864</v>
+        <v>0.01901664147690712</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6085714285714285</v>
+        <v>0.5874285714285714</v>
       </c>
       <c r="W6" t="n">
-        <v>0.009897433186107876</v>
+        <v>0.01779704171702561</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6098775510204082</v>
+        <v>0.5954938775510205</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.009026634146923073</v>
+        <v>0.01757059078700478</v>
       </c>
     </row>
     <row r="7">
@@ -996,7 +996,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1023,58 +1023,58 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6196697893827652</v>
+        <v>0.6041234314495487</v>
       </c>
       <c r="I7" t="n">
-        <v>0.008072667384815473</v>
+        <v>0.02059079513146542</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6125714285714287</v>
+        <v>0.5874285714285714</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0123882762221022</v>
+        <v>0.01779704171702561</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6160625235166147</v>
+        <v>0.5956269772817006</v>
       </c>
       <c r="M7" t="n">
-        <v>0.009005442112081687</v>
+        <v>0.01855125039611551</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6308539944903581</v>
+        <v>0.6159779614325068</v>
       </c>
       <c r="O7" t="n">
-        <v>0.005153798053407684</v>
+        <v>0.01375342800701559</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6303030303030303</v>
+        <v>0.6027548209366391</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.00678994905998143</v>
+        <v>0.0166888498411691</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6269027941755214</v>
+        <v>0.6049901613537976</v>
       </c>
       <c r="S7" t="n">
-        <v>0.005095134608681723</v>
+        <v>0.01475456867549878</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6232380952380953</v>
+        <v>0.616</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01347879833424135</v>
+        <v>0.01901664147690712</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6125714285714287</v>
+        <v>0.5874285714285714</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0123882762221022</v>
+        <v>0.01779704171702561</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6137469387755102</v>
+        <v>0.5954938775510205</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01166065611419298</v>
+        <v>0.01757059078700478</v>
       </c>
     </row>
     <row r="8">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1112,58 +1112,58 @@
         <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6280441457767039</v>
+        <v>0.5827563528669661</v>
       </c>
       <c r="I8" t="n">
-        <v>0.007193477742145323</v>
+        <v>0.0182116151187019</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6114285714285714</v>
+        <v>0.5897142857142856</v>
       </c>
       <c r="K8" t="n">
-        <v>0.006998542122237635</v>
+        <v>0.01099164803524078</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6195711255053723</v>
+        <v>0.5861063368879279</v>
       </c>
       <c r="M8" t="n">
-        <v>0.002903146606150238</v>
+        <v>0.01218200652780122</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6104683195592286</v>
+        <v>0.5987603305785123</v>
       </c>
       <c r="O8" t="n">
-        <v>0.008623953632230612</v>
+        <v>0.01112210977310539</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6071625344352618</v>
+        <v>0.5876033057851241</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01260161213386513</v>
+        <v>0.01207102055107802</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6044155844155843</v>
+        <v>0.5883116883116882</v>
       </c>
       <c r="S8" t="n">
-        <v>0.009389817551878465</v>
+        <v>0.01120369113369845</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6274285714285714</v>
+        <v>0.6168571428571429</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0118837910531917</v>
+        <v>0.0122224283635471</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6114285714285714</v>
+        <v>0.5897142857142856</v>
       </c>
       <c r="W8" t="n">
-        <v>0.006998542122237635</v>
+        <v>0.01099164803524078</v>
       </c>
       <c r="X8" t="n">
-        <v>0.6144163265306123</v>
+        <v>0.596478911564626</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.005593488343738903</v>
+        <v>0.01089333982797329</v>
       </c>
     </row>
     <row r="9">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1201,57 +1201,769 @@
         <v>5</v>
       </c>
       <c r="H9" t="n">
+        <v>0.5827563528669661</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.0182116151187019</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.5897142857142856</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.01099164803524078</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.5861063368879279</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.01218200652780122</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.5987603305785123</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.01112210977310539</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.5876033057851241</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.01207102055107802</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.5883116883116882</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.01120369113369845</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.6168571428571429</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.0122224283635471</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.5897142857142856</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.01099164803524078</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.596478911564626</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.01089333982797329</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.6085131776978114</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.01900074019798977</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.6047058823529412</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.01341382853057812</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.6065466457884552</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.01505052797827696</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.6192837465564739</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.01369121062235724</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.6214876033057851</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.01206315925389064</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.6167493112947657</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.01255545719988956</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.6109803921568627</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.01509931239857134</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.6047058823529412</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.01341382853057812</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.6034509803921567</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.01361128961271437</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.6085131776978114</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.01900074019798977</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.6047058823529412</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.01341382853057812</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.6065466457884552</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.01505052797827696</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.6192837465564739</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.01369121062235724</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.6214876033057851</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.01206315925389064</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.6167493112947657</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.01255545719988956</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.6109803921568627</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.01509931239857134</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.6047058823529412</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.01341382853057812</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.6034509803921567</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.01361128961271437</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>5</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.6089705445422638</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.01801028558349509</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.6058823529411764</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.0110048746669822</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.6073734320064142</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.01350946643807132</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.6060606060606062</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.0151515151515151</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.6090909090909091</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.01300905669765022</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.6031404958677685</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.01341346048639007</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.6115686274509804</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.01517867441059154</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.6058823529411764</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.0110048746669822</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.6032941176470588</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.01222812761462815</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>5</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.6089705445422638</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.01801028558349509</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.6058823529411764</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.0110048746669822</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.6073734320064142</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.01350946643807132</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.6060606060606062</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.0151515151515151</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.6090909090909091</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.01300905669765022</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.6031404958677685</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.01341346048639007</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.6115686274509804</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.01517867441059154</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.6058823529411764</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.0110048746669822</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.6032941176470588</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.01222812761462815</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>4</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.6183372367284565</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.008663292355168311</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.6085714285714285</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.009897433186107876</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.6133829977006118</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.007763048768872636</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.6291322314049587</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.003956310362629474</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.6287878787878788</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.006794604493548555</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.625491932310114</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.004619919287070238</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.6190476190476191</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.0111879429756864</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.6085714285714285</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.009897433186107876</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.6098775510204082</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.009026634146923073</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.6196697893827652</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.008072667384815473</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.6125714285714287</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.0123882762221022</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.6160625235166147</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.009005442112081687</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.6308539944903581</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.005153798053407684</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.6303030303030303</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.00678994905998143</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.6269027941755214</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.005095134608681723</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.6232380952380953</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.01347879833424135</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.6125714285714287</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.0123882762221022</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.6137469387755102</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.01166065611419298</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>5</v>
+      </c>
+      <c r="H16" t="n">
         <v>0.6280441457767039</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I16" t="n">
         <v>0.007193477742145323</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J16" t="n">
         <v>0.6114285714285714</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K16" t="n">
         <v>0.006998542122237635</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L16" t="n">
         <v>0.6195711255053723</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M16" t="n">
         <v>0.002903146606150238</v>
       </c>
-      <c r="N9" t="n">
+      <c r="N16" t="n">
         <v>0.6104683195592286</v>
       </c>
-      <c r="O9" t="n">
+      <c r="O16" t="n">
         <v>0.008623953632230612</v>
       </c>
-      <c r="P9" t="n">
+      <c r="P16" t="n">
         <v>0.6071625344352618</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="Q16" t="n">
         <v>0.01260161213386513</v>
       </c>
-      <c r="R9" t="n">
+      <c r="R16" t="n">
         <v>0.6044155844155843</v>
       </c>
-      <c r="S9" t="n">
+      <c r="S16" t="n">
         <v>0.009389817551878465</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T16" t="n">
         <v>0.6274285714285714</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U16" t="n">
         <v>0.0118837910531917</v>
       </c>
-      <c r="V9" t="n">
+      <c r="V16" t="n">
         <v>0.6114285714285714</v>
       </c>
-      <c r="W9" t="n">
+      <c r="W16" t="n">
         <v>0.006998542122237635</v>
       </c>
-      <c r="X9" t="n">
+      <c r="X16" t="n">
         <v>0.6144163265306123</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="Y16" t="n">
+        <v>0.005593488343738903</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.6280441457767039</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.007193477742145323</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.6114285714285714</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.006998542122237635</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.6195711255053723</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.002903146606150238</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.6104683195592286</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.008623953632230612</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.6071625344352618</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.01260161213386513</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.6044155844155843</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.009389817551878465</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.6274285714285714</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.0118837910531917</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.6114285714285714</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.006998542122237635</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.6144163265306123</v>
+      </c>
+      <c r="Y17" t="n">
         <v>0.005593488343738903</v>
       </c>
     </row>

--- a/analysis/aggregate/multiset-PRF.xlsx
+++ b/analysis/aggregate/multiset-PRF.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -578,58 +578,58 @@
         <v>5</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5896153400840919</v>
+        <v>0.5893764859242134</v>
       </c>
       <c r="I2" t="n">
-        <v>0.008927634446055845</v>
+        <v>0.01741708870596326</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5847058823529412</v>
+        <v>0.5835294117647059</v>
       </c>
       <c r="K2" t="n">
-        <v>0.007892004626469874</v>
+        <v>0.006443794794178469</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5871284510430088</v>
+        <v>0.5863740502636061</v>
       </c>
       <c r="M2" t="n">
-        <v>0.007398071636777081</v>
+        <v>0.01104429315306361</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6027548209366392</v>
+        <v>0.6088154269972452</v>
       </c>
       <c r="O2" t="n">
-        <v>0.010149935772419</v>
+        <v>0.00897961763802013</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6022038567493113</v>
+        <v>0.6090909090909091</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.009661530532644701</v>
+        <v>0.006489927817845653</v>
       </c>
       <c r="R2" t="n">
-        <v>0.5978512396694213</v>
+        <v>0.6050137741046832</v>
       </c>
       <c r="S2" t="n">
-        <v>0.009775539445164426</v>
+        <v>0.007985180059179982</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5958823529411765</v>
+        <v>0.5915686274509804</v>
       </c>
       <c r="U2" t="n">
-        <v>0.008752436910064981</v>
+        <v>0.01029645164950283</v>
       </c>
       <c r="V2" t="n">
-        <v>0.5847058823529412</v>
+        <v>0.5835294117647059</v>
       </c>
       <c r="W2" t="n">
-        <v>0.007892004626469874</v>
+        <v>0.006443794794178469</v>
       </c>
       <c r="X2" t="n">
-        <v>0.5848627450980393</v>
+        <v>0.5826666666666667</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.008087373691482448</v>
+        <v>0.008251151865809356</v>
       </c>
     </row>
     <row r="3">
@@ -650,75 +650,75 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>5</v>
       </c>
       <c r="H3" t="n">
-        <v>0.557504926942833</v>
+        <v>0.5819327495506192</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01676012661093303</v>
+        <v>0.01350551509231377</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5588235294117647</v>
+        <v>0.5776470588235294</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01764705882352943</v>
+        <v>0.008724939396583146</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5581565311300726</v>
+        <v>0.5797283288997976</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01706725013505337</v>
+        <v>0.009464949202304861</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5753443526170801</v>
+        <v>0.5840220385674932</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01838726897627025</v>
+        <v>0.01251095187643591</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5771349862258953</v>
+        <v>0.5809917355371901</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01573506840054526</v>
+        <v>0.01368428011792811</v>
       </c>
       <c r="R3" t="n">
-        <v>0.5658559622195984</v>
+        <v>0.578953168044077</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01689606040553306</v>
+        <v>0.01258142133465254</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5742156862745097</v>
+        <v>0.5890196078431372</v>
       </c>
       <c r="U3" t="n">
-        <v>0.02243577702541931</v>
+        <v>0.008330449327940394</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5588235294117647</v>
+        <v>0.5776470588235294</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01764705882352943</v>
+        <v>0.008724939396583146</v>
       </c>
       <c r="X3" t="n">
-        <v>0.5527002801120446</v>
+        <v>0.5786666666666667</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.01958351431853355</v>
+        <v>0.008228755574244085</v>
       </c>
     </row>
     <row r="4">
@@ -744,7 +744,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -756,58 +756,58 @@
         <v>5</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5740157127939933</v>
+        <v>0.5916901681611542</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0165149354316568</v>
+        <v>0.02016787668242784</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5705882352941176</v>
+        <v>0.5858823529411765</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01440876319284219</v>
+        <v>0.01533929977694739</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5722928044339168</v>
+        <v>0.5887107083770676</v>
       </c>
       <c r="M4" t="n">
-        <v>0.01539271601654646</v>
+        <v>0.0165621510088697</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5757575757575759</v>
+        <v>0.6090909090909091</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02116018112360495</v>
+        <v>0.02069327164374777</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5694214876033058</v>
+        <v>0.6079889807162535</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.02101623264216045</v>
+        <v>0.02161700809653369</v>
       </c>
       <c r="R4" t="n">
-        <v>0.5682093663911845</v>
+        <v>0.6041322314049586</v>
       </c>
       <c r="S4" t="n">
-        <v>0.02090544290305585</v>
+        <v>0.02070701980492139</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5880392156862745</v>
+        <v>0.5972549019607843</v>
       </c>
       <c r="U4" t="n">
-        <v>0.01641095647739284</v>
+        <v>0.01748839347081165</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5705882352941176</v>
+        <v>0.5858823529411765</v>
       </c>
       <c r="W4" t="n">
-        <v>0.01440876319284219</v>
+        <v>0.01533929977694739</v>
       </c>
       <c r="X4" t="n">
-        <v>0.5738039215686274</v>
+        <v>0.5861960784313724</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.01540782267601536</v>
+        <v>0.01596902037345472</v>
       </c>
     </row>
     <row r="5">
@@ -838,65 +838,65 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5344662936228443</v>
+        <v>0.5770503819409216</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02067948964304349</v>
+        <v>0.01252672325279868</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5388235294117647</v>
+        <v>0.5764705882352941</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02020654592625613</v>
+        <v>0.01860163329510809</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5366236925916494</v>
+        <v>0.5767453463330888</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0202264023160756</v>
+        <v>0.01549336477976942</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5546005509641875</v>
+        <v>0.5807162534435263</v>
       </c>
       <c r="O5" t="n">
-        <v>0.02262155057937219</v>
+        <v>0.02587186089669179</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5476584022038569</v>
+        <v>0.5793388429752067</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.02453569788125821</v>
+        <v>0.02384949533116468</v>
       </c>
       <c r="R5" t="n">
-        <v>0.541806375442739</v>
+        <v>0.5759779614325068</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0231798487821793</v>
+        <v>0.02443760645434908</v>
       </c>
       <c r="T5" t="n">
-        <v>0.562078431372549</v>
+        <v>0.5862745098039215</v>
       </c>
       <c r="U5" t="n">
-        <v>0.02061825542443885</v>
+        <v>0.0212882850496161</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5388235294117647</v>
+        <v>0.5764705882352941</v>
       </c>
       <c r="W5" t="n">
-        <v>0.02020654592625613</v>
+        <v>0.01860163329510809</v>
       </c>
       <c r="X5" t="n">
-        <v>0.537268907563025</v>
+        <v>0.576392156862745</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.01989914172312257</v>
+        <v>0.01943927541554152</v>
       </c>
     </row>
     <row r="6">
@@ -934,58 +934,58 @@
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6041234314495487</v>
+        <v>0.5885729901346457</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02059079513146542</v>
+        <v>0.01434578166638185</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5874285714285714</v>
+        <v>0.5771428571428572</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01779704171702561</v>
+        <v>0.01895214165917371</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5956269772817006</v>
+        <v>0.5827489838483214</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01855125039611551</v>
+        <v>0.01572591562002584</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6159779614325068</v>
+        <v>0.5982093663911846</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01375342800701559</v>
+        <v>0.01902123564292455</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6027548209366391</v>
+        <v>0.5900826446280992</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0166888498411691</v>
+        <v>0.02202995699561951</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6049901613537976</v>
+        <v>0.5896340023612751</v>
       </c>
       <c r="S6" t="n">
-        <v>0.01475456867549878</v>
+        <v>0.0197476624434779</v>
       </c>
       <c r="T6" t="n">
-        <v>0.616</v>
+        <v>0.5997142857142856</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01901664147690712</v>
+        <v>0.01499659825372654</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5874285714285714</v>
+        <v>0.5771428571428572</v>
       </c>
       <c r="W6" t="n">
-        <v>0.01779704171702561</v>
+        <v>0.01895214165917371</v>
       </c>
       <c r="X6" t="n">
-        <v>0.5954938775510205</v>
+        <v>0.5823074829931973</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.01757059078700478</v>
+        <v>0.01581143688590221</v>
       </c>
     </row>
     <row r="7">
@@ -1011,70 +1011,70 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6041234314495487</v>
+        <v>0.5921537011135863</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02059079513146542</v>
+        <v>0.01572927167731297</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5874285714285714</v>
+        <v>0.576</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01779704171702561</v>
+        <v>0.01954586443027092</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5956269772817006</v>
+        <v>0.5839582632896159</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01855125039611551</v>
+        <v>0.0176783953204371</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6159779614325068</v>
+        <v>0.5865013774104684</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01375342800701559</v>
+        <v>0.0161265885861902</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6027548209366391</v>
+        <v>0.5735537190082647</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0166888498411691</v>
+        <v>0.01846963117560518</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6049901613537976</v>
+        <v>0.5751593860684768</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01475456867549878</v>
+        <v>0.01691080750840531</v>
       </c>
       <c r="T7" t="n">
-        <v>0.616</v>
+        <v>0.6072380952380952</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01901664147690712</v>
+        <v>0.01645236372406243</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5874285714285714</v>
+        <v>0.576</v>
       </c>
       <c r="W7" t="n">
-        <v>0.01779704171702561</v>
+        <v>0.01954586443027092</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5954938775510205</v>
+        <v>0.5847020408163266</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01757059078700478</v>
+        <v>0.01775442331957868</v>
       </c>
     </row>
     <row r="8">
@@ -1095,12 +1095,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1112,58 +1112,58 @@
         <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5827563528669661</v>
+        <v>0.6044888400595519</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0182116151187019</v>
+        <v>0.02502233032196416</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5897142857142856</v>
+        <v>0.590857142857143</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01099164803524078</v>
+        <v>0.03012897446048928</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5861063368879279</v>
+        <v>0.5975812189851615</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01218200652780122</v>
+        <v>0.02761008091364495</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5987603305785123</v>
+        <v>0.6125895316804406</v>
       </c>
       <c r="O8" t="n">
-        <v>0.01112210977310539</v>
+        <v>0.02081385265014823</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5876033057851241</v>
+        <v>0.6046831955922866</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01207102055107802</v>
+        <v>0.02162578301392225</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5883116883116882</v>
+        <v>0.6039866194411647</v>
       </c>
       <c r="S8" t="n">
-        <v>0.01120369113369845</v>
+        <v>0.02106077805006582</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6168571428571429</v>
+        <v>0.6152571428571428</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0122224283635471</v>
+        <v>0.02838194309552378</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5897142857142856</v>
+        <v>0.590857142857143</v>
       </c>
       <c r="W8" t="n">
-        <v>0.01099164803524078</v>
+        <v>0.03012897446048928</v>
       </c>
       <c r="X8" t="n">
-        <v>0.596478911564626</v>
+        <v>0.5966503401360546</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.01089333982797329</v>
+        <v>0.02963822214866865</v>
       </c>
     </row>
     <row r="9">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1194,65 +1194,65 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G9" t="n">
         <v>5</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5827563528669661</v>
+        <v>0.5902150849845075</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0182116151187019</v>
+        <v>0.01810002716136684</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5897142857142856</v>
+        <v>0.5794285714285714</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01099164803524078</v>
+        <v>0.02160876617278751</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5861063368879279</v>
+        <v>0.5847190269177354</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01218200652780122</v>
+        <v>0.01896366872255571</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5987603305785123</v>
+        <v>0.5852617079889807</v>
       </c>
       <c r="O9" t="n">
-        <v>0.01112210977310539</v>
+        <v>0.01676682560798752</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5876033057851241</v>
+        <v>0.5738292011019285</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.01207102055107802</v>
+        <v>0.01992727863785874</v>
       </c>
       <c r="R9" t="n">
-        <v>0.5883116883116882</v>
+        <v>0.574970484061393</v>
       </c>
       <c r="S9" t="n">
-        <v>0.01120369113369845</v>
+        <v>0.01837290192878885</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6168571428571429</v>
+        <v>0.6084761904761905</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0122224283635471</v>
+        <v>0.0153987071342336</v>
       </c>
       <c r="V9" t="n">
-        <v>0.5897142857142856</v>
+        <v>0.5794285714285714</v>
       </c>
       <c r="W9" t="n">
-        <v>0.01099164803524078</v>
+        <v>0.02160876617278751</v>
       </c>
       <c r="X9" t="n">
-        <v>0.596478911564626</v>
+        <v>0.5878149659863946</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.01089333982797329</v>
+        <v>0.01867418582817036</v>
       </c>
     </row>
     <row r="10">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1290,58 +1290,58 @@
         <v>5</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6085131776978114</v>
+        <v>0.5948542072015077</v>
       </c>
       <c r="I10" t="n">
-        <v>0.01900074019798977</v>
+        <v>0.01480386202464196</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6047058823529412</v>
+        <v>0.5894117647058824</v>
       </c>
       <c r="K10" t="n">
-        <v>0.01341382853057812</v>
+        <v>0.01832048412046755</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6065466457884552</v>
+        <v>0.59179938677253</v>
       </c>
       <c r="M10" t="n">
-        <v>0.01505052797827696</v>
+        <v>0.006659585244265088</v>
       </c>
       <c r="N10" t="n">
-        <v>0.6192837465564739</v>
+        <v>0.6077134986225896</v>
       </c>
       <c r="O10" t="n">
-        <v>0.01369121062235724</v>
+        <v>0.009053265413308574</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6214876033057851</v>
+        <v>0.6099173553719008</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.01206315925389064</v>
+        <v>0.01340412190160093</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6167493112947657</v>
+        <v>0.6046280991735536</v>
       </c>
       <c r="S10" t="n">
-        <v>0.01255545719988956</v>
+        <v>0.008110129206841111</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6109803921568627</v>
+        <v>0.5970588235294118</v>
       </c>
       <c r="U10" t="n">
-        <v>0.01509931239857134</v>
+        <v>0.008985442539129081</v>
       </c>
       <c r="V10" t="n">
-        <v>0.6047058823529412</v>
+        <v>0.5894117647058824</v>
       </c>
       <c r="W10" t="n">
-        <v>0.01341382853057812</v>
+        <v>0.01832048412046755</v>
       </c>
       <c r="X10" t="n">
-        <v>0.6034509803921567</v>
+        <v>0.5881176470588234</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.01361128961271437</v>
+        <v>0.01118128551255112</v>
       </c>
     </row>
     <row r="11">
@@ -1362,75 +1362,75 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G11" t="n">
         <v>5</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6085131776978114</v>
+        <v>0.5952638467659841</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01900074019798977</v>
+        <v>0.008821336791440457</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6047058823529412</v>
+        <v>0.6</v>
       </c>
       <c r="K11" t="n">
-        <v>0.01341382853057812</v>
+        <v>0.01100487466698223</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6065466457884552</v>
+        <v>0.5975248847321126</v>
       </c>
       <c r="M11" t="n">
-        <v>0.01505052797827696</v>
+        <v>0.005207844720491532</v>
       </c>
       <c r="N11" t="n">
-        <v>0.6192837465564739</v>
+        <v>0.5976584022038568</v>
       </c>
       <c r="O11" t="n">
-        <v>0.01369121062235724</v>
+        <v>0.01199217568026379</v>
       </c>
       <c r="P11" t="n">
-        <v>0.6214876033057851</v>
+        <v>0.6005509641873278</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.01206315925389064</v>
+        <v>0.01299446436922395</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6167493112947657</v>
+        <v>0.5956237701692246</v>
       </c>
       <c r="S11" t="n">
-        <v>0.01255545719988956</v>
+        <v>0.01240017317175393</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6109803921568627</v>
+        <v>0.6040196078431372</v>
       </c>
       <c r="U11" t="n">
-        <v>0.01509931239857134</v>
+        <v>0.01008422813382262</v>
       </c>
       <c r="V11" t="n">
-        <v>0.6047058823529412</v>
+        <v>0.6</v>
       </c>
       <c r="W11" t="n">
-        <v>0.01341382853057812</v>
+        <v>0.01100487466698223</v>
       </c>
       <c r="X11" t="n">
-        <v>0.6034509803921567</v>
+        <v>0.5977927170868347</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.01361128961271437</v>
+        <v>0.009594203513843866</v>
       </c>
     </row>
     <row r="12">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1468,58 +1468,58 @@
         <v>5</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6089705445422638</v>
+        <v>0.6093434232018645</v>
       </c>
       <c r="I12" t="n">
-        <v>0.01801028558349509</v>
+        <v>0.01036162439621699</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6058823529411764</v>
+        <v>0.6035294117647059</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0110048746669822</v>
+        <v>0.005261336417646588</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6073734320064142</v>
+        <v>0.6064082259568042</v>
       </c>
       <c r="M12" t="n">
-        <v>0.01350946643807132</v>
+        <v>0.007479113694365483</v>
       </c>
       <c r="N12" t="n">
-        <v>0.6060606060606062</v>
+        <v>0.6201101928374657</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0151515151515151</v>
+        <v>0.009999279015361679</v>
       </c>
       <c r="P12" t="n">
-        <v>0.6090909090909091</v>
+        <v>0.6217630853994491</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.01300905669765022</v>
+        <v>0.005299003873738715</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6031404958677685</v>
+        <v>0.617190082644628</v>
       </c>
       <c r="S12" t="n">
-        <v>0.01341346048639007</v>
+        <v>0.00797614624038826</v>
       </c>
       <c r="T12" t="n">
-        <v>0.6115686274509804</v>
+        <v>0.6092156862745097</v>
       </c>
       <c r="U12" t="n">
-        <v>0.01517867441059154</v>
+        <v>0.01211885265910783</v>
       </c>
       <c r="V12" t="n">
-        <v>0.6058823529411764</v>
+        <v>0.6035294117647059</v>
       </c>
       <c r="W12" t="n">
-        <v>0.0110048746669822</v>
+        <v>0.005261336417646588</v>
       </c>
       <c r="X12" t="n">
-        <v>0.6032941176470588</v>
+        <v>0.6014901960784312</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.01222812761462815</v>
+        <v>0.008982874902974674</v>
       </c>
     </row>
     <row r="13">
@@ -1550,65 +1550,65 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G13" t="n">
         <v>5</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6089705445422638</v>
+        <v>0.6058924812421129</v>
       </c>
       <c r="I13" t="n">
-        <v>0.01801028558349509</v>
+        <v>0.0109477061602439</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6058823529411764</v>
+        <v>0.6094117647058823</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0110048746669822</v>
+        <v>0.009843059135695055</v>
       </c>
       <c r="L13" t="n">
-        <v>0.6073734320064142</v>
+        <v>0.607632487010589</v>
       </c>
       <c r="M13" t="n">
-        <v>0.01350946643807132</v>
+        <v>0.009858756210419886</v>
       </c>
       <c r="N13" t="n">
-        <v>0.6060606060606062</v>
+        <v>0.6052341597796145</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0151515151515151</v>
+        <v>0.009219394231780489</v>
       </c>
       <c r="P13" t="n">
-        <v>0.6090909090909091</v>
+        <v>0.6157024793388429</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.01300905669765022</v>
+        <v>0.01160626690520161</v>
       </c>
       <c r="R13" t="n">
-        <v>0.6031404958677685</v>
+        <v>0.6059504132231405</v>
       </c>
       <c r="S13" t="n">
-        <v>0.01341346048639007</v>
+        <v>0.0102570385219809</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6115686274509804</v>
+        <v>0.6056862745098039</v>
       </c>
       <c r="U13" t="n">
-        <v>0.01517867441059154</v>
+        <v>0.00809640110669118</v>
       </c>
       <c r="V13" t="n">
-        <v>0.6058823529411764</v>
+        <v>0.6094117647058823</v>
       </c>
       <c r="W13" t="n">
-        <v>0.0110048746669822</v>
+        <v>0.009843059135695055</v>
       </c>
       <c r="X13" t="n">
-        <v>0.6032941176470588</v>
+        <v>0.6023529411764705</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.01222812761462815</v>
+        <v>0.008582772011074158</v>
       </c>
     </row>
     <row r="14">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1643,61 +1643,61 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6183372367284565</v>
+        <v>0.6180631467047127</v>
       </c>
       <c r="I14" t="n">
-        <v>0.008663292355168311</v>
+        <v>0.0142604907374553</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6085714285714285</v>
+        <v>0.6102857142857143</v>
       </c>
       <c r="K14" t="n">
-        <v>0.009897433186107876</v>
+        <v>0.0142284566834157</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6133829977006118</v>
+        <v>0.6141449158819897</v>
       </c>
       <c r="M14" t="n">
-        <v>0.007763048768872636</v>
+        <v>0.01411802260491624</v>
       </c>
       <c r="N14" t="n">
-        <v>0.6291322314049587</v>
+        <v>0.6258953168044077</v>
       </c>
       <c r="O14" t="n">
-        <v>0.003956310362629474</v>
+        <v>0.01279583929751358</v>
       </c>
       <c r="P14" t="n">
-        <v>0.6287878787878788</v>
+        <v>0.6223140495867769</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.006794604493548555</v>
+        <v>0.01651169901211124</v>
       </c>
       <c r="R14" t="n">
-        <v>0.625491932310114</v>
+        <v>0.6200708382526564</v>
       </c>
       <c r="S14" t="n">
-        <v>0.004619919287070238</v>
+        <v>0.01500235796637535</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6190476190476191</v>
+        <v>0.6249523809523809</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0111879429756864</v>
+        <v>0.01088800959011637</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6085714285714285</v>
+        <v>0.6102857142857143</v>
       </c>
       <c r="W14" t="n">
-        <v>0.009897433186107876</v>
+        <v>0.0142284566834157</v>
       </c>
       <c r="X14" t="n">
-        <v>0.6098775510204082</v>
+        <v>0.6127183673469387</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.009026634146923073</v>
+        <v>0.01275676324783244</v>
       </c>
     </row>
     <row r="15">
@@ -1718,75 +1718,75 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G15" t="n">
         <v>5</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6196697893827652</v>
+        <v>0.6133456582061744</v>
       </c>
       <c r="I15" t="n">
-        <v>0.008072667384815473</v>
+        <v>0.008220477921809861</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6125714285714287</v>
+        <v>0.6091428571428572</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0123882762221022</v>
+        <v>0.009561828874675127</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6160625235166147</v>
+        <v>0.6112301889825578</v>
       </c>
       <c r="M15" t="n">
-        <v>0.009005442112081687</v>
+        <v>0.008632278338325375</v>
       </c>
       <c r="N15" t="n">
-        <v>0.6308539944903581</v>
+        <v>0.6048209366391184</v>
       </c>
       <c r="O15" t="n">
-        <v>0.005153798053407684</v>
+        <v>0.0115489111935287</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6303030303030303</v>
+        <v>0.6016528925619835</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.00678994905998143</v>
+        <v>0.01174439324919676</v>
       </c>
       <c r="R15" t="n">
-        <v>0.6269027941755214</v>
+        <v>0.5993309720582447</v>
       </c>
       <c r="S15" t="n">
-        <v>0.005095134608681723</v>
+        <v>0.01163565403963791</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6232380952380953</v>
+        <v>0.6231428571428571</v>
       </c>
       <c r="U15" t="n">
-        <v>0.01347879833424135</v>
+        <v>0.008475655413823604</v>
       </c>
       <c r="V15" t="n">
-        <v>0.6125714285714287</v>
+        <v>0.6091428571428572</v>
       </c>
       <c r="W15" t="n">
-        <v>0.0123882762221022</v>
+        <v>0.009561828874675127</v>
       </c>
       <c r="X15" t="n">
-        <v>0.6137469387755102</v>
+        <v>0.6115265306122449</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.01166065611419298</v>
+        <v>0.008614073808233622</v>
       </c>
     </row>
     <row r="16">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1824,58 +1824,58 @@
         <v>5</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6280441457767039</v>
+        <v>0.6272984057833638</v>
       </c>
       <c r="I16" t="n">
-        <v>0.007193477742145323</v>
+        <v>0.0165968106504594</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6114285714285714</v>
+        <v>0.6068571428571429</v>
       </c>
       <c r="K16" t="n">
-        <v>0.006998542122237635</v>
+        <v>0.004780914437337572</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6195711255053723</v>
+        <v>0.6168008310407948</v>
       </c>
       <c r="M16" t="n">
-        <v>0.002903146606150238</v>
+        <v>0.007760230392511242</v>
       </c>
       <c r="N16" t="n">
-        <v>0.6104683195592286</v>
+        <v>0.6325068870523416</v>
       </c>
       <c r="O16" t="n">
-        <v>0.008623953632230612</v>
+        <v>0.01767706581504751</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6071625344352618</v>
+        <v>0.6272727272727273</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.01260161213386513</v>
+        <v>0.009167802364900167</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6044155844155843</v>
+        <v>0.6258480913026367</v>
       </c>
       <c r="S16" t="n">
-        <v>0.009389817551878465</v>
+        <v>0.01298550430696496</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6274285714285714</v>
+        <v>0.6262857142857143</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0118837910531917</v>
+        <v>0.01167589528097291</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6114285714285714</v>
+        <v>0.6068571428571429</v>
       </c>
       <c r="W16" t="n">
-        <v>0.006998542122237635</v>
+        <v>0.004780914437337572</v>
       </c>
       <c r="X16" t="n">
-        <v>0.6144163265306123</v>
+        <v>0.6109496598639457</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.005593488343738903</v>
+        <v>0.004817233474699134</v>
       </c>
     </row>
     <row r="17">
@@ -1906,65 +1906,65 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G17" t="n">
         <v>5</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6280441457767039</v>
+        <v>0.6264125436516107</v>
       </c>
       <c r="I17" t="n">
-        <v>0.007193477742145323</v>
+        <v>0.01588998828994154</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6114285714285714</v>
+        <v>0.6068571428571429</v>
       </c>
       <c r="K17" t="n">
-        <v>0.006998542122237635</v>
+        <v>0.009389529557231414</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6195711255053723</v>
+        <v>0.6164127611737201</v>
       </c>
       <c r="M17" t="n">
-        <v>0.002903146606150238</v>
+        <v>0.01064560881261912</v>
       </c>
       <c r="N17" t="n">
-        <v>0.6104683195592286</v>
+        <v>0.6108815426997245</v>
       </c>
       <c r="O17" t="n">
-        <v>0.008623953632230612</v>
+        <v>0.01665755733119532</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6071625344352618</v>
+        <v>0.6052341597796145</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.01260161213386513</v>
+        <v>0.01773599846040761</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6044155844155843</v>
+        <v>0.6041086186540732</v>
       </c>
       <c r="S17" t="n">
-        <v>0.009389817551878465</v>
+        <v>0.01708853837187769</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6274285714285714</v>
+        <v>0.6256190476190476</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0118837910531917</v>
+        <v>0.01075600343888586</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6114285714285714</v>
+        <v>0.6068571428571429</v>
       </c>
       <c r="W17" t="n">
-        <v>0.006998542122237635</v>
+        <v>0.009389529557231414</v>
       </c>
       <c r="X17" t="n">
-        <v>0.6144163265306123</v>
+        <v>0.6114938775510204</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.005593488343738903</v>
+        <v>0.008812664058283159</v>
       </c>
     </row>
   </sheetData>
